--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2212,6 +2212,1030 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130227494</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>517019</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6610848</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130226965</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>517224</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6610919</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130227469</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>517018</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6610851</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130227461</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>517062</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6610903</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130226160</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gusselby, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>517341</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6610964</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130225522</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92073</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516943</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6610768</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130226285</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Slöjsmossen, Slöjsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>517393</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6610934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130226063</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58113</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gusselby, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>517292</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6610939</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130236552</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slöjsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>517288</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6610968</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>aktivitet färska spår</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>130099642</v>
       </c>
       <c r="B13" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>130099642</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130098634</v>
       </c>
       <c r="B14" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130098037</v>
       </c>
       <c r="B15" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>130227494</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>130226965</v>
       </c>
       <c r="B17" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>130227469</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>130227461</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>130226160</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>130225522</v>
       </c>
       <c r="B21" t="n">
-        <v>92073</v>
+        <v>92160</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130226285</v>
       </c>
       <c r="B22" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>130226063</v>
       </c>
       <c r="B23" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>130236552</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>130099642</v>
       </c>
       <c r="B13" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>130226965</v>
       </c>
       <c r="B17" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>130227461</v>
       </c>
       <c r="B19" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>130225522</v>
       </c>
       <c r="B21" t="n">
-        <v>92160</v>
+        <v>92163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>130099642</v>
       </c>
       <c r="B13" t="n">
-        <v>91113</v>
+        <v>91139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,32 +1980,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130098634</v>
+        <v>130098037</v>
       </c>
       <c r="B14" t="n">
-        <v>58198</v>
+        <v>58011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
         <v>6610859</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130098037</v>
+        <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,27 +2108,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517203</v>
+        <v>517019</v>
       </c>
       <c r="R15" t="n">
-        <v>6610859</v>
+        <v>6610848</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2167,22 +2167,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,71 +2193,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130227494</v>
+        <v>130226965</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>93039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517019</v>
+        <v>517224</v>
       </c>
       <c r="R16" t="n">
-        <v>6610848</v>
+        <v>6610919</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2299,7 +2289,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,48 +2316,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130226965</v>
+        <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>93013</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517224</v>
+        <v>517018</v>
       </c>
       <c r="R17" t="n">
-        <v>6610919</v>
+        <v>6610851</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2394,19 +2392,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,22 +2409,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130227469</v>
+        <v>130227461</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>91757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,45 +2432,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517018</v>
+        <v>517062</v>
       </c>
       <c r="R18" t="n">
-        <v>6610851</v>
+        <v>6610903</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2509,9 +2489,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,22 +2516,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130227461</v>
+        <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>91731</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,37 +2539,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Gusselby, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517062</v>
+        <v>517341</v>
       </c>
       <c r="R19" t="n">
-        <v>6610903</v>
+        <v>6610964</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2613,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,69 +2629,89 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130226160</v>
+        <v>130225522</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>92189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gusselby, Lindes sn, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517341</v>
+        <v>516943</v>
       </c>
       <c r="R20" t="n">
-        <v>6610964</v>
+        <v>6610768</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2720,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2730,12 +2750,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,89 +2761,69 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130225522</v>
+        <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>92163</v>
+        <v>58011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Slöjsmossen, Slöjsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516943</v>
+        <v>517393</v>
       </c>
       <c r="R21" t="n">
-        <v>6610768</v>
+        <v>6610934</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,7 +2852,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,7 +2862,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,26 +2873,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130226285</v>
+        <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57985</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,42 +2905,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slöjsmossen, Slöjsmossen, Vstm</t>
+          <t>Slöjsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517393</v>
+        <v>517288</v>
       </c>
       <c r="R22" t="n">
-        <v>6610934</v>
+        <v>6610968</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,19 +2970,14 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>aktivitet färska spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,31 +2988,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130226063</v>
+        <v>130098634</v>
       </c>
       <c r="B23" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,14 +3040,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gusselby, Lindes sn, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517292</v>
+        <v>517203</v>
       </c>
       <c r="R23" t="n">
-        <v>6610939</v>
+        <v>6610859</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3081,22 +3074,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,27 +3121,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130236552</v>
+        <v>130226063</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>58224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3157,27 +3150,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slöjsmossen, Vstm</t>
+          <t>Gusselby, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517288</v>
+        <v>517292</v>
       </c>
       <c r="R24" t="n">
-        <v>6610968</v>
+        <v>6610939</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,14 +3194,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>aktivitet färska spår</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,16 +3217,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -2212,7 +2212,7 @@
         <v>130226965</v>
       </c>
       <c r="B16" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130227461</v>
       </c>
       <c r="B18" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>130225522</v>
       </c>
       <c r="B20" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -2212,7 +2212,7 @@
         <v>130226965</v>
       </c>
       <c r="B16" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130227461</v>
       </c>
       <c r="B18" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>130225522</v>
       </c>
       <c r="B20" t="n">
-        <v>92190</v>
+        <v>92191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>130226965</v>
       </c>
       <c r="B16" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>130227461</v>
       </c>
       <c r="B18" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>130225522</v>
       </c>
       <c r="B20" t="n">
-        <v>92191</v>
+        <v>92193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>130098634</v>
       </c>
       <c r="B23" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>130226063</v>
       </c>
       <c r="B24" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -2212,7 +2212,7 @@
         <v>130226965</v>
       </c>
       <c r="B16" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>130225522</v>
       </c>
       <c r="B20" t="n">
-        <v>92193</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130098037</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130098037</v>
       </c>
       <c r="B14" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130098037</v>
       </c>
       <c r="B14" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130098037</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130226285</v>
       </c>
       <c r="B21" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130095566</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130227494</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130227469</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>130226160</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>130236552</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112442386</v>
+        <v>130225522</v>
       </c>
       <c r="B2" t="n">
-        <v>90937</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långängen, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517192</v>
+        <v>516943</v>
       </c>
       <c r="R2" t="n">
-        <v>6610916</v>
+        <v>6610768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112442383</v>
+        <v>112442377</v>
       </c>
       <c r="B3" t="n">
-        <v>89617</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517062</v>
+        <v>517001</v>
       </c>
       <c r="R3" t="n">
-        <v>6610905</v>
+        <v>6610770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112442387</v>
+        <v>130095566</v>
       </c>
       <c r="B4" t="n">
-        <v>90914</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +890,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långängen, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517205</v>
+        <v>517047</v>
       </c>
       <c r="R4" t="n">
-        <v>6610904</v>
+        <v>6610773</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,16 +980,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,12 +1024,7 @@
         <v>112442376</v>
       </c>
       <c r="B5" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,7 +1068,7 @@
         <v>517225</v>
       </c>
       <c r="R5" t="n">
-        <v>6610750</v>
+        <v>6610749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,37 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112442380</v>
+        <v>112442381</v>
       </c>
       <c r="B6" t="n">
-        <v>90269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516963</v>
+        <v>517053</v>
       </c>
       <c r="R6" t="n">
-        <v>6610866</v>
+        <v>6610906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,37 +1225,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112442388</v>
+        <v>112442382</v>
       </c>
       <c r="B7" t="n">
-        <v>89067</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517245</v>
+        <v>517063</v>
       </c>
       <c r="R7" t="n">
-        <v>6610894</v>
+        <v>6610905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,15 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112442382</v>
+        <v>130227461</v>
       </c>
       <c r="B8" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långängen, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517063</v>
+        <v>517062</v>
       </c>
       <c r="R8" t="n">
-        <v>6610906</v>
+        <v>6610903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,12 +1387,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,12 +1417,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1403,16 +1432,11 @@
         <v>112442385</v>
       </c>
       <c r="B9" t="n">
-        <v>90914</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1440,7 +1464,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517172</v>
+        <v>517173</v>
       </c>
       <c r="R9" t="n">
         <v>6610926</v>
@@ -1502,15 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112442381</v>
+        <v>112442387</v>
       </c>
       <c r="B10" t="n">
-        <v>89653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517053</v>
+        <v>517205</v>
       </c>
       <c r="R10" t="n">
-        <v>6610906</v>
+        <v>6610904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,50 +1623,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112442377</v>
+        <v>130226965</v>
       </c>
       <c r="B11" t="n">
-        <v>89617</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långängen, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517000</v>
+        <v>517224</v>
       </c>
       <c r="R11" t="n">
-        <v>6610770</v>
+        <v>6610919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,12 +1688,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,65 +1718,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130095566</v>
+        <v>112442383</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Långängen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517047</v>
+        <v>517062</v>
       </c>
       <c r="R12" t="n">
-        <v>6610773</v>
+        <v>6610904</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,27 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:44</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hack i död gran</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,51 +1811,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130099642</v>
+        <v>112442388</v>
       </c>
       <c r="B13" t="n">
-        <v>91139</v>
+        <v>91282</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,17 +1858,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Långängen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517260</v>
+        <v>517245</v>
       </c>
       <c r="R13" t="n">
-        <v>6610925</v>
+        <v>6610894</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,22 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,94 +1908,64 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130098037</v>
+        <v>130099642</v>
       </c>
       <c r="B14" t="n">
-        <v>58050</v>
+        <v>91282</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517203</v>
+        <v>517260</v>
       </c>
       <c r="R14" t="n">
-        <v>6610859</v>
+        <v>6610925</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,6 +2019,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2097,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130227494</v>
+        <v>112442386</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,39 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Långängen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517019</v>
+        <v>517192</v>
       </c>
       <c r="R15" t="n">
-        <v>6610848</v>
+        <v>6610916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,22 +2121,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,22 +2141,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130226965</v>
+        <v>112442380</v>
       </c>
       <c r="B16" t="n">
-        <v>93047</v>
+        <v>92567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Långängen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517224</v>
+        <v>516963</v>
       </c>
       <c r="R16" t="n">
-        <v>6610919</v>
+        <v>6610866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,22 +2218,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,32 +2232,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130227469</v>
+        <v>130226160</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2345,27 +2280,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Gusselby, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517018</v>
+        <v>517341</v>
       </c>
       <c r="R17" t="n">
-        <v>6610851</v>
+        <v>6610964</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,11 +2324,26 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2405,64 +2352,97 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130227461</v>
+        <v>130227469</v>
       </c>
       <c r="B18" t="n">
-        <v>91761</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517062</v>
+        <v>517018</v>
       </c>
       <c r="R18" t="n">
-        <v>6610903</v>
+        <v>6610851</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2489,19 +2469,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,26 +2486,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130226160</v>
+        <v>130227494</v>
       </c>
       <c r="B19" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2564,17 +2534,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gusselby, Lindes sn, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517341</v>
+        <v>517019</v>
       </c>
       <c r="R19" t="n">
-        <v>6610964</v>
+        <v>6610848</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2603,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,12 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,51 +2594,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130225522</v>
+        <v>130228461</v>
       </c>
       <c r="B20" t="n">
-        <v>92199</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,37 +2621,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516943</v>
+        <v>516853</v>
       </c>
       <c r="R20" t="n">
-        <v>6610768</v>
+        <v>6610804</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2738,19 +2686,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,65 +2703,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130226285</v>
+        <v>130236552</v>
       </c>
       <c r="B21" t="n">
-        <v>58050</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slöjsmossen, Slöjsmossen, Vstm</t>
+          <t>Slöjsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517393</v>
+        <v>517288</v>
       </c>
       <c r="R21" t="n">
-        <v>6610934</v>
+        <v>6610968</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2850,19 +2791,14 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>aktivitet färska spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,48 +2809,43 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236552</v>
+        <v>130098634</v>
       </c>
       <c r="B22" t="n">
-        <v>57889</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2923,27 +2854,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slöjsmossen, Vstm</t>
+          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517288</v>
+        <v>517203</v>
       </c>
       <c r="R22" t="n">
-        <v>6610968</v>
+        <v>6610859</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,17 +2895,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>aktivitet färska spår</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,26 +2921,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130098634</v>
+        <v>130226063</v>
       </c>
       <c r="B23" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3040,14 +2978,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kattgubbens sjö, Kattgubbens sjö, Vstm</t>
+          <t>Gusselby, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517203</v>
+        <v>517292</v>
       </c>
       <c r="R23" t="n">
-        <v>6610859</v>
+        <v>6610939</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3074,22 +3012,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,32 +3059,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130226063</v>
+        <v>130226285</v>
       </c>
       <c r="B24" t="n">
-        <v>58256</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3157,14 +3095,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gusselby, Lindes sn, Vstm</t>
+          <t>Slöjsmossen, Slöjsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517292</v>
+        <v>517393</v>
       </c>
       <c r="R24" t="n">
-        <v>6610939</v>
+        <v>6610934</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3196,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3206,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55016-2025 artfynd.xlsx
+++ b/artfynd/A 55016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442382</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442385</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226965</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442377</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442383</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442388</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130099642</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442386</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442380</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130095566</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226160</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227469</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227494</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2605,6 +2695,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228461</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130236552</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098634</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2949,6 +3054,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226063</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,6 +3176,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226285</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,8 +3288,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>